--- a/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_18h00_timeseries.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>13.8</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -792,7 +792,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>17</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="30" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -511,8 +511,8 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9">
-        <v>13.9</v>
+      <c r="D9" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -582,7 +582,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -596,7 +596,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>16.3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -708,7 +708,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>14</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>16.3</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="26" spans="1:4">
